--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="162">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -479,6 +479,10 @@
   </si>
   <si>
     <t>fr-lm-observation-assessment.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Site de l'observation</t>
@@ -3093,13 +3097,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3167,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3196,10 +3200,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3250,7 +3254,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3267,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3296,10 +3300,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3350,7 +3354,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3367,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3393,13 +3397,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3450,7 +3454,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3467,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3493,13 +3497,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3550,7 +3554,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-observation-assessment.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-observation-assessment.header.langue</t>
+    <t>fr-lm-observation-assessment.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-observation-assessment.observationDate[x]</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="161">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,10 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut de l'évaluation</t>
+  </si>
+  <si>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -846,8 +843,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2503,7 +2500,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2533,31 +2530,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2571,10 +2568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2600,10 +2597,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2654,7 +2651,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2671,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2700,10 +2697,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2754,7 +2751,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2771,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2797,13 +2794,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2854,7 +2851,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2871,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2900,10 +2897,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2954,7 +2951,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2971,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3000,10 +2997,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3054,7 +3051,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3071,10 +3068,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3097,13 +3094,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3154,7 +3151,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3171,10 +3168,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3200,10 +3197,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3254,7 +3251,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3271,10 +3268,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3300,10 +3297,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3354,7 +3351,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3371,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3397,13 +3394,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>158</v>
-      </c>
       <c r="M26" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3454,7 +3451,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3471,10 +3468,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3497,13 +3494,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3554,7 +3551,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-assessment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
